--- a/academias/Biología - Estadisticos 20211.xlsx
+++ b/academias/Biología - Estadisticos 20211.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="27">
   <si>
     <t>Docente</t>
   </si>
@@ -57,6 +57,9 @@
     <t>Flores Ovalle Victor</t>
   </si>
   <si>
+    <t>Martínez Cruz Norma</t>
+  </si>
+  <si>
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
@@ -69,16 +72,16 @@
     <t>3BLCM</t>
   </si>
   <si>
+    <t>3ARHV</t>
+  </si>
+  <si>
+    <t>3ASV</t>
+  </si>
+  <si>
+    <t>3ALCV</t>
+  </si>
+  <si>
     <t>3APV</t>
-  </si>
-  <si>
-    <t>3ARHV</t>
-  </si>
-  <si>
-    <t>3ASV</t>
-  </si>
-  <si>
-    <t>3ALCV</t>
   </si>
   <si>
     <t>3AEM</t>
@@ -498,10 +501,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2">
         <v>25</v>
@@ -533,10 +536,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3">
         <v>32</v>
@@ -568,10 +571,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4">
         <v>35</v>
@@ -603,28 +606,28 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G5">
-        <v>57.14</v>
+        <v>80</v>
       </c>
       <c r="H5">
-        <v>42.86</v>
+        <v>20</v>
       </c>
       <c r="I5">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -638,28 +641,28 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>80</v>
+        <v>57.14</v>
       </c>
       <c r="H6">
-        <v>20</v>
+        <v>42.86</v>
       </c>
       <c r="I6">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -670,31 +673,31 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7">
+        <v>31</v>
+      </c>
+      <c r="E7">
         <v>21</v>
       </c>
-      <c r="E7">
-        <v>12</v>
-      </c>
       <c r="F7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>57.14</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="H7">
-        <v>42.86</v>
+        <v>32.26</v>
       </c>
       <c r="I7">
-        <v>6.2</v>
+        <v>7.1</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -705,31 +708,31 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8">
+        <v>21</v>
+      </c>
+      <c r="E8">
         <v>12</v>
       </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8">
-        <v>31</v>
-      </c>
-      <c r="E8">
-        <v>21</v>
-      </c>
       <c r="F8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>67.73999999999999</v>
+        <v>57.14</v>
       </c>
       <c r="H8">
-        <v>32.26</v>
+        <v>42.86</v>
       </c>
       <c r="I8">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -740,48 +743,48 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9">
         <v>36</v>
       </c>
       <c r="E9">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F9">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G9">
-        <v>52.78</v>
+        <v>63.89</v>
       </c>
       <c r="H9">
-        <v>47.22</v>
+        <v>36.11</v>
       </c>
       <c r="I9">
-        <v>6.8</v>
+        <v>6.1</v>
       </c>
       <c r="J9">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>47.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10">
         <v>39</v>
@@ -810,72 +813,72 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D11">
         <v>36</v>
       </c>
       <c r="E11">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11">
-        <v>88.89</v>
+        <v>91.67</v>
       </c>
       <c r="H11">
-        <v>11.11</v>
+        <v>8.33</v>
       </c>
       <c r="I11">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="J11">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>11.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D12">
         <v>33</v>
       </c>
       <c r="E12">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F12">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G12">
-        <v>48.48</v>
+        <v>63.64</v>
       </c>
       <c r="H12">
-        <v>51.52</v>
+        <v>36.36</v>
       </c>
       <c r="I12">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="J12">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>51.52</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -932,31 +935,34 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2">
         <v>25</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="H2">
-        <v>100</v>
+        <v>28</v>
+      </c>
+      <c r="I2">
+        <v>7.6</v>
       </c>
       <c r="J2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -964,31 +970,34 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3">
         <v>32</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H3">
-        <v>100</v>
+        <v>12.5</v>
+      </c>
+      <c r="I3">
+        <v>8.5</v>
       </c>
       <c r="J3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -996,31 +1005,34 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4">
         <v>35</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F4">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="H4">
-        <v>100</v>
+        <v>31.43</v>
+      </c>
+      <c r="I4">
+        <v>7.9</v>
       </c>
       <c r="J4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1028,31 +1040,34 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="H5">
-        <v>100</v>
+        <v>8.57</v>
+      </c>
+      <c r="I5">
+        <v>8.699999999999999</v>
       </c>
       <c r="J5">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1060,19 +1075,19 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1081,7 +1096,7 @@
         <v>100</v>
       </c>
       <c r="J6">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="K6">
         <v>100</v>
@@ -1089,194 +1104,212 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7">
+        <v>31</v>
+      </c>
+      <c r="E7">
         <v>19</v>
       </c>
-      <c r="C7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>21</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
       <c r="F7">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>61.29</v>
       </c>
       <c r="H7">
-        <v>100</v>
+        <v>38.71</v>
+      </c>
+      <c r="I7">
+        <v>8.4</v>
       </c>
       <c r="J7">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>38.71</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F8">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>76.19</v>
       </c>
       <c r="H8">
-        <v>100</v>
+        <v>23.81</v>
+      </c>
+      <c r="I8">
+        <v>8.300000000000001</v>
       </c>
       <c r="J8">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9">
         <v>36</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F9">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>38.89</v>
       </c>
       <c r="H9">
-        <v>100</v>
+        <v>61.11</v>
+      </c>
+      <c r="I9">
+        <v>7.9</v>
       </c>
       <c r="J9">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="K9">
-        <v>100</v>
+        <v>61.11</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10">
         <v>39</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F10">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H10">
-        <v>100</v>
+        <v>35.9</v>
+      </c>
+      <c r="I10">
+        <v>8.300000000000001</v>
       </c>
       <c r="J10">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="K10">
-        <v>100</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D11">
         <v>36</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F11">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>61.11</v>
       </c>
       <c r="H11">
-        <v>100</v>
+        <v>38.89</v>
+      </c>
+      <c r="I11">
+        <v>8.5</v>
       </c>
       <c r="J11">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>38.89</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D12">
         <v>33</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F12">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>33.33</v>
       </c>
       <c r="H12">
-        <v>100</v>
+        <v>66.67</v>
+      </c>
+      <c r="I12">
+        <v>8.1</v>
       </c>
       <c r="J12">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="K12">
-        <v>100</v>
+        <v>66.67</v>
       </c>
     </row>
   </sheetData>
@@ -1333,28 +1366,28 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2">
         <v>25</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="H2">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="I2">
-        <v>6.4</v>
+        <v>7.1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1368,28 +1401,28 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3">
         <v>32</v>
       </c>
       <c r="E3">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>68.75</v>
+        <v>87.5</v>
       </c>
       <c r="H3">
-        <v>31.25</v>
+        <v>12.5</v>
       </c>
       <c r="I3">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1403,28 +1436,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4">
         <v>35</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>48.57</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="H4">
-        <v>51.43</v>
+        <v>31.43</v>
       </c>
       <c r="I4">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1438,28 +1471,28 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>57.14</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="H5">
-        <v>42.86</v>
+        <v>8.57</v>
       </c>
       <c r="I5">
-        <v>6.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1473,28 +1506,28 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>80</v>
+        <v>57.14</v>
       </c>
       <c r="H6">
-        <v>20</v>
+        <v>42.86</v>
       </c>
       <c r="I6">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1505,31 +1538,31 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E7">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G7">
-        <v>57.14</v>
+        <v>74.19</v>
       </c>
       <c r="H7">
-        <v>42.86</v>
+        <v>25.81</v>
       </c>
       <c r="I7">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1540,31 +1573,31 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E8">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G8">
-        <v>67.73999999999999</v>
+        <v>76.19</v>
       </c>
       <c r="H8">
-        <v>32.26</v>
+        <v>23.81</v>
       </c>
       <c r="I8">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1575,66 +1608,66 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9">
         <v>36</v>
       </c>
       <c r="E9">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F9">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G9">
-        <v>52.78</v>
+        <v>66.67</v>
       </c>
       <c r="H9">
-        <v>47.22</v>
+        <v>33.33</v>
       </c>
       <c r="I9">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J9">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>47.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10">
         <v>39</v>
       </c>
       <c r="E10">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G10">
-        <v>87.18000000000001</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H10">
-        <v>12.82</v>
+        <v>10.26</v>
       </c>
       <c r="I10">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1645,72 +1678,72 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D11">
         <v>36</v>
       </c>
       <c r="E11">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11">
-        <v>88.89</v>
+        <v>91.67</v>
       </c>
       <c r="H11">
-        <v>11.11</v>
+        <v>8.33</v>
       </c>
       <c r="I11">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>11.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D12">
         <v>33</v>
       </c>
       <c r="E12">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F12">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G12">
-        <v>48.48</v>
+        <v>63.64</v>
       </c>
       <c r="H12">
-        <v>51.52</v>
+        <v>36.36</v>
       </c>
       <c r="I12">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="J12">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>51.52</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Biología - Estadisticos 20211.xlsx
+++ b/academias/Biología - Estadisticos 20211.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
     <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
-    <sheet name="3er Parcial" sheetId="3" r:id="rId3"/>
+    <sheet name="Final" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -103,6 +103,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -155,8 +159,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -457,42 +463,45 @@
   <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -515,19 +524,19 @@
       <c r="F2">
         <v>11</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>56</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>44</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>6.4</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -550,19 +559,19 @@
       <c r="F3">
         <v>10</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>68.75</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>31.25</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>6.8</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>0</v>
       </c>
     </row>
@@ -585,19 +594,19 @@
       <c r="F4">
         <v>18</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>48.57</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>51.43</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>6.5</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -620,19 +629,19 @@
       <c r="F5">
         <v>7</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>80</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>20</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>7.2</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>0</v>
       </c>
     </row>
@@ -655,19 +664,19 @@
       <c r="F6">
         <v>9</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>57.14</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>42.86</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>6.2</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -690,19 +699,19 @@
       <c r="F7">
         <v>10</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>67.73999999999999</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>32.26</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>7.1</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>0</v>
       </c>
     </row>
@@ -725,19 +734,19 @@
       <c r="F8">
         <v>9</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>57.14</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>42.86</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>6.7</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>0</v>
       </c>
     </row>
@@ -760,19 +769,19 @@
       <c r="F9">
         <v>13</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>63.89</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>36.11</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>6.1</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>0</v>
       </c>
     </row>
@@ -795,19 +804,19 @@
       <c r="F10">
         <v>5</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>87.18000000000001</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>12.82</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>7.7</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0</v>
       </c>
     </row>
@@ -830,19 +839,19 @@
       <c r="F11">
         <v>3</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>91.67</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>8.33</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>7.8</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>0</v>
       </c>
     </row>
@@ -865,19 +874,19 @@
       <c r="F12">
         <v>12</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>63.64</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>36.36</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>6.2</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>0</v>
       </c>
     </row>
@@ -891,42 +900,45 @@
   <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -949,19 +961,19 @@
       <c r="F2">
         <v>7</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>72</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>28</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>7.6</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -984,19 +996,19 @@
       <c r="F3">
         <v>4</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>87.5</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>12.5</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>8.5</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1019,19 +1031,19 @@
       <c r="F4">
         <v>11</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>68.56999999999999</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>31.43</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>7.9</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1054,19 +1066,19 @@
       <c r="F5">
         <v>3</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>91.43000000000001</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>8.57</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>8.699999999999999</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1089,16 +1101,16 @@
       <c r="F6">
         <v>21</v>
       </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
         <v>100</v>
       </c>
       <c r="J6">
         <v>21</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>100</v>
       </c>
     </row>
@@ -1121,19 +1133,19 @@
       <c r="F7">
         <v>12</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>61.29</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>38.71</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>8.4</v>
       </c>
       <c r="J7">
         <v>12</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>38.71</v>
       </c>
     </row>
@@ -1156,19 +1168,19 @@
       <c r="F8">
         <v>5</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>76.19</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>23.81</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>8.300000000000001</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1191,19 +1203,19 @@
       <c r="F9">
         <v>22</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>38.89</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>61.11</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>7.9</v>
       </c>
       <c r="J9">
         <v>22</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>61.11</v>
       </c>
     </row>
@@ -1226,19 +1238,19 @@
       <c r="F10">
         <v>14</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>64.09999999999999</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>35.9</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>8.300000000000001</v>
       </c>
       <c r="J10">
         <v>14</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>35.9</v>
       </c>
     </row>
@@ -1261,19 +1273,19 @@
       <c r="F11">
         <v>14</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>61.11</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>38.89</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>8.5</v>
       </c>
       <c r="J11">
         <v>14</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>38.89</v>
       </c>
     </row>
@@ -1296,19 +1308,19 @@
       <c r="F12">
         <v>22</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>33.33</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>66.67</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>8.1</v>
       </c>
       <c r="J12">
         <v>22</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>66.67</v>
       </c>
     </row>
@@ -1322,42 +1334,45 @@
   <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1380,19 +1395,19 @@
       <c r="F2">
         <v>7</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>72</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>28</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>7.1</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1415,19 +1430,19 @@
       <c r="F3">
         <v>4</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>87.5</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>12.5</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>7.8</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1450,19 +1465,19 @@
       <c r="F4">
         <v>11</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>68.56999999999999</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>31.43</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>7.5</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1485,19 +1500,19 @@
       <c r="F5">
         <v>3</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>91.43000000000001</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>8.57</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1520,19 +1535,19 @@
       <c r="F6">
         <v>9</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>57.14</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>42.86</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>6.2</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1555,19 +1570,19 @@
       <c r="F7">
         <v>8</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>74.19</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>25.81</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>7.4</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1590,19 +1605,19 @@
       <c r="F8">
         <v>5</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>76.19</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>23.81</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>7.7</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1625,19 +1640,19 @@
       <c r="F9">
         <v>12</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>66.67</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>33.33</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>6.4</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1660,19 +1675,19 @@
       <c r="F10">
         <v>4</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>89.73999999999999</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>10.26</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>7.8</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1695,19 +1710,19 @@
       <c r="F11">
         <v>3</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>91.67</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>8.33</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>8</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1730,19 +1745,19 @@
       <c r="F12">
         <v>12</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>63.64</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>36.36</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>6.5</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>0</v>
       </c>
     </row>

--- a/academias/Biología - Estadisticos 20211.xlsx
+++ b/academias/Biología - Estadisticos 20211.xlsx
@@ -104,7 +104,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="2">

--- a/academias/Biología - Estadisticos 20211.xlsx
+++ b/academias/Biología - Estadisticos 20211.xlsx
@@ -1096,22 +1096,25 @@
         <v>21</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>33.33</v>
+      </c>
+      <c r="I6" s="2">
+        <v>7.1</v>
       </c>
       <c r="J6">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1303,25 +1306,25 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F12">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G12" s="1">
-        <v>33.33</v>
+        <v>51.52</v>
       </c>
       <c r="H12" s="1">
-        <v>66.67</v>
+        <v>48.48</v>
       </c>
       <c r="I12" s="2">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="J12">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="K12" s="1">
-        <v>66.67</v>
+        <v>42.42</v>
       </c>
     </row>
   </sheetData>
@@ -1530,19 +1533,19 @@
         <v>21</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G6" s="1">
-        <v>57.14</v>
+        <v>66.67</v>
       </c>
       <c r="H6" s="1">
-        <v>42.86</v>
+        <v>33.33</v>
       </c>
       <c r="I6" s="2">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1740,19 +1743,19 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F12">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G12" s="1">
-        <v>63.64</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>36.36</v>
+        <v>24.24</v>
       </c>
       <c r="I12" s="2">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="J12">
         <v>0</v>

--- a/academias/Biología - Estadisticos 20211.xlsx
+++ b/academias/Biología - Estadisticos 20211.xlsx
@@ -1201,25 +1201,25 @@
         <v>36</v>
       </c>
       <c r="E9">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F9">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G9" s="1">
-        <v>38.89</v>
+        <v>50</v>
       </c>
       <c r="H9" s="1">
-        <v>61.11</v>
+        <v>50</v>
       </c>
       <c r="I9" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J9">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K9" s="1">
-        <v>61.11</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1236,25 +1236,25 @@
         <v>39</v>
       </c>
       <c r="E10">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F10">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G10" s="1">
-        <v>64.09999999999999</v>
+        <v>69.23</v>
       </c>
       <c r="H10" s="1">
-        <v>35.9</v>
+        <v>30.77</v>
       </c>
       <c r="I10" s="2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J10">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K10" s="1">
-        <v>35.9</v>
+        <v>30.77</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1271,25 +1271,25 @@
         <v>36</v>
       </c>
       <c r="E11">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F11">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G11" s="1">
-        <v>61.11</v>
+        <v>66.67</v>
       </c>
       <c r="H11" s="1">
-        <v>38.89</v>
+        <v>33.33</v>
       </c>
       <c r="I11" s="2">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J11">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K11" s="1">
-        <v>38.89</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1306,25 +1306,25 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F12">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G12" s="1">
-        <v>51.52</v>
+        <v>54.55</v>
       </c>
       <c r="H12" s="1">
-        <v>48.48</v>
+        <v>45.45</v>
       </c>
       <c r="I12" s="2">
         <v>7.5</v>
       </c>
       <c r="J12">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K12" s="1">
-        <v>42.42</v>
+        <v>39.39</v>
       </c>
     </row>
   </sheetData>
@@ -1638,19 +1638,19 @@
         <v>36</v>
       </c>
       <c r="E9">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F9">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G9" s="1">
-        <v>66.67</v>
+        <v>77.78</v>
       </c>
       <c r="H9" s="1">
-        <v>33.33</v>
+        <v>22.22</v>
       </c>
       <c r="I9" s="2">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1673,19 +1673,19 @@
         <v>39</v>
       </c>
       <c r="E10">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1">
-        <v>89.73999999999999</v>
+        <v>94.87</v>
       </c>
       <c r="H10" s="1">
-        <v>10.26</v>
+        <v>5.13</v>
       </c>
       <c r="I10" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J10">
         <v>0</v>

--- a/academias/Biología - Estadisticos 20211.xlsx
+++ b/academias/Biología - Estadisticos 20211.xlsx
@@ -1131,25 +1131,25 @@
         <v>31</v>
       </c>
       <c r="E7">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F7">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G7" s="1">
-        <v>61.29</v>
+        <v>74.19</v>
       </c>
       <c r="H7" s="1">
-        <v>38.71</v>
+        <v>25.81</v>
       </c>
       <c r="I7" s="2">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="J7">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>38.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1201,25 +1201,25 @@
         <v>36</v>
       </c>
       <c r="E9">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F9">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G9" s="1">
-        <v>50</v>
+        <v>69.44</v>
       </c>
       <c r="H9" s="1">
-        <v>50</v>
+        <v>30.56</v>
       </c>
       <c r="I9" s="2">
-        <v>7.7</v>
+        <v>6.5</v>
       </c>
       <c r="J9">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1236,25 +1236,25 @@
         <v>39</v>
       </c>
       <c r="E10">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F10">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1">
-        <v>69.23</v>
+        <v>94.87</v>
       </c>
       <c r="H10" s="1">
-        <v>30.77</v>
+        <v>5.13</v>
       </c>
       <c r="I10" s="2">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="J10">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>30.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1271,25 +1271,25 @@
         <v>36</v>
       </c>
       <c r="E11">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F11">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>66.67</v>
+        <v>91.67</v>
       </c>
       <c r="H11" s="1">
-        <v>33.33</v>
+        <v>8.33</v>
       </c>
       <c r="I11" s="2">
-        <v>8.300000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="J11">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1306,25 +1306,25 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F12">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G12" s="1">
-        <v>54.55</v>
+        <v>66.67</v>
       </c>
       <c r="H12" s="1">
-        <v>45.45</v>
+        <v>33.33</v>
       </c>
       <c r="I12" s="2">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
       <c r="J12">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>39.39</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1393,19 +1393,19 @@
         <v>25</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G2" s="1">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="H2" s="1">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I2" s="2">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1428,19 +1428,19 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1463,16 +1463,16 @@
         <v>35</v>
       </c>
       <c r="E4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F4">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G4" s="1">
-        <v>68.56999999999999</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>31.43</v>
+        <v>25.71</v>
       </c>
       <c r="I4" s="2">
         <v>7.5</v>
@@ -1498,19 +1498,19 @@
         <v>35</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" s="1">
-        <v>91.43000000000001</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>8.57</v>
+        <v>11.43</v>
       </c>
       <c r="I5" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1533,19 +1533,19 @@
         <v>21</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>66.67</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>33.33</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1568,19 +1568,19 @@
         <v>31</v>
       </c>
       <c r="E7">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>74.19</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>25.81</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1603,19 +1603,19 @@
         <v>21</v>
       </c>
       <c r="E8">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>76.19</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>23.81</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1638,19 +1638,19 @@
         <v>36</v>
       </c>
       <c r="E9">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F9">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G9" s="1">
-        <v>77.78</v>
+        <v>66.67</v>
       </c>
       <c r="H9" s="1">
-        <v>22.22</v>
+        <v>33.33</v>
       </c>
       <c r="I9" s="2">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1673,19 +1673,19 @@
         <v>39</v>
       </c>
       <c r="E10">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G10" s="1">
-        <v>94.87</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>5.13</v>
+        <v>10.26</v>
       </c>
       <c r="I10" s="2">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1708,19 +1708,19 @@
         <v>36</v>
       </c>
       <c r="E11">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G11" s="1">
-        <v>91.67</v>
+        <v>86.11</v>
       </c>
       <c r="H11" s="1">
-        <v>8.33</v>
+        <v>13.89</v>
       </c>
       <c r="I11" s="2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1743,19 +1743,19 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F12">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G12" s="1">
-        <v>75.76000000000001</v>
+        <v>51.52</v>
       </c>
       <c r="H12" s="1">
-        <v>24.24</v>
+        <v>48.48</v>
       </c>
       <c r="I12" s="2">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J12">
         <v>0</v>
